--- a/Result/checksun/橡膠工業.xlsx
+++ b/Result/checksun/橡膠工業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,29 +773,29 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7117,24 +7117,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10289,24 +10289,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>-2.0</t>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13461,24 +13461,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>-3.0</t>
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -13666,12 +13666,12 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13749,24 +13749,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14901,99 +14901,99 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>24.5075</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>24.619</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>-19.56</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>24.5075</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>24.619</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>-19.56</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD51" t="inlineStr">
         <is>
           <t>-41.91</t>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15189,99 +15189,99 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>24.54</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>24.632</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>-20.94</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>24.54</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>24.632</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>-20.94</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD52" t="inlineStr">
         <is>
           <t>-22.33</t>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -15970,12 +15970,12 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16053,99 +16053,99 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>24.61</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>24.664</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>-17.14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>24.61</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>24.664</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>-17.14</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD55" t="inlineStr">
         <is>
           <t>-74.97</t>
@@ -16233,7 +16233,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>287</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16583,7 +16583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -16838,12 +16838,12 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -16951,12 +16951,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -17414,12 +17414,12 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -18103,12 +18103,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -18278,12 +18278,12 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -18967,12 +18967,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>341</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>54.21</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -19755,7 +19755,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19805,29 +19805,29 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -19835,12 +19835,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -20411,12 +20411,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -20699,12 +20699,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -20987,12 +20987,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>124470</t>
+          <t>123498</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -22927,7 +22927,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -23007,12 +23007,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -23182,12 +23182,12 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -23295,12 +23295,12 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -23470,12 +23470,12 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -23583,12 +23583,12 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -23758,12 +23758,12 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -24046,12 +24046,12 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -24159,12 +24159,12 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -24334,12 +24334,12 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -24447,12 +24447,12 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -24622,12 +24622,12 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -24735,12 +24735,12 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -24910,12 +24910,12 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -25023,12 +25023,12 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -25198,12 +25198,12 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -25311,12 +25311,12 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -25486,12 +25486,12 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -25599,12 +25599,12 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -25774,12 +25774,12 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>-9.5</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -25887,12 +25887,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -26062,12 +26062,12 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -26099,7 +26099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -26179,12 +26179,12 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -26467,12 +26467,12 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -26755,12 +26755,12 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -27043,12 +27043,12 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -27331,12 +27331,12 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -27619,12 +27619,12 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -27907,12 +27907,12 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -28082,7 +28082,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -28195,12 +28195,12 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -28483,12 +28483,12 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -28771,12 +28771,12 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -29059,12 +29059,12 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>375</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -29271,7 +29271,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -29351,12 +29351,12 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
@@ -29526,12 +29526,12 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
@@ -29609,7 +29609,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -29639,12 +29639,12 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -29744,7 +29744,7 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -29814,12 +29814,12 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -29927,12 +29927,12 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -30102,12 +30102,12 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
@@ -30122,7 +30122,7 @@
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -30215,12 +30215,12 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -30390,12 +30390,12 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
@@ -30410,7 +30410,7 @@
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -30503,12 +30503,12 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -30678,12 +30678,12 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -30698,7 +30698,7 @@
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -30791,12 +30791,12 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -30966,12 +30966,12 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -31079,12 +31079,12 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -31254,12 +31254,12 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
@@ -31274,7 +31274,7 @@
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -31367,12 +31367,12 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -31655,12 +31655,12 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -31830,12 +31830,12 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -31943,12 +31943,12 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -32118,12 +32118,12 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
@@ -32201,7 +32201,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -32231,12 +32231,12 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>497</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>103.38</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
@@ -32624,7 +32624,7 @@
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -32912,7 +32912,7 @@
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -34064,7 +34064,7 @@
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -34352,7 +34352,7 @@
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -35216,7 +35216,7 @@
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">

--- a/Result/checksun/橡膠工業.xlsx
+++ b/Result/checksun/橡膠工業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32441,7 +32841,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -32729,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33017,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -33305,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -33593,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -33881,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -34169,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -34457,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/橡膠工業.xlsx
+++ b/Result/checksun/橡膠工業.xlsx
@@ -1011,15 +1011,11 @@
           <t>33.435</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>32.319</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>32.68062500000001</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>32.319</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>32.68062500000001</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>33.235</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>32.322</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>32.700625</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>32.322</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>32.700625</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>33.00750000000001</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>32.311</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>32.72625</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>32.311</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>32.72625</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>32.78250000000001</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>32.292</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>32.7575</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>32.292</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>32.7575</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>32.56</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>32.268</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>32.7875</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>32.268</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>32.7875</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>32.3575</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>32.249</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>32.816875</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>32.249</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>32.816875</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>32.0975</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>32.21100000000001</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>32.8275</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>32.21100000000001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>32.8275</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>31.785</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>32.173</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>32.826875</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>32.173</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>32.826875</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>31.575</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>32.152</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>32.152</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>32.85</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>31.3475</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>32.125</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>32.8625</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>32.125</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>32.8625</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>90.25</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>91.206</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>90.57374999999999</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>91.206</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>90.57375</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>90.25</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>91.25399999999999</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>90.56875</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>91.254</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>90.56874999999999</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>90.265</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>91.29599999999999</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>90.56125</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>91.29600000000001</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>90.56125</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>90.25</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>91.314</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>90.54625000000001</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>91.31399999999999</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>90.54625</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>90.235</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>91.33800000000001</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>90.535</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>91.33799999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>90.535</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>90.24</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>91.34200000000001</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>90.5275</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>91.342</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>90.5275</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>90.275</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>91.34</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>90.52250000000001</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>90.52249999999999</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>90.26</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>91.32799999999999</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>90.51500000000001</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>91.328</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>90.515</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>90.235</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>91.32</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>90.51124999999999</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>90.51125</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>90.175</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>91.292</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>90.49125000000001</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>91.292</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>90.49124999999999</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>15.25</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.903</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>16.058125</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>15.903</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>16.058125</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>15.28</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.928</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>16.074375</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>15.928</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>16.074375</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>15.315</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.954</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>16.0925</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>15.954</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>16.0925</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>15.35</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>15.976</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>16.110625</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>15.976</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>16.110625</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>15.4075</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>15.998</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>16.1275</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>15.998</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>16.1275</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>15.4675</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>16.019</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>16.145625</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>16.019</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>16.145625</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>15.53</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>16.04</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>16.16375</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>16.16375</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>16.063</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>16.184375</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>16.063</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>16.184375</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>15.65</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>16.088</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>16.20375</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>16.088</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>16.20375</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>15.7075</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>16.109</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>16.2225</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>16.109</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>16.2225</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>23.2025</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.83</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>23.75</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>23.265</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.86</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>23.77125</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>23.77125</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>23.3075</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.877</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>23.7925</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>23.877</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>23.7925</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>23.35</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>23.889</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>23.81375</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>23.889</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>23.81375</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>23.3925</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>23.904</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>23.833125</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>23.904</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>23.833125</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>23.41</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>23.908</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>23.843125</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>23.908</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>23.843125</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>23.4225</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>23.905</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>23.848125</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>23.905</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>23.848125</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>23.4375</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>23.915</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>23.8525</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>23.915</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>23.8525</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>23.46</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>23.931</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>23.861875</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>23.931</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>23.861875</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>23.4675</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>23.8675</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>23.8675</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>23.9275</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>24.024</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>24.268125</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>24.024</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>24.268125</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>23.935</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>24.041</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>24.279375</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>24.041</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>24.279375</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>23.935</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>24.057</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>24.29125</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>24.057</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>24.29125</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>23.93</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>24.067</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>24.3025</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>24.067</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>24.3025</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>23.9325</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>24.083</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>24.31375</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>24.083</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>24.31375</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>23.93</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>24.095</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>24.325</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>24.095</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>24.325</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>23.93</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>24.106</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>24.335625</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>24.106</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>24.335625</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>23.9275</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>24.116</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>24.34625</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>24.116</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>24.34625</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>23.9375</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>24.13</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>24.355</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>24.355</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>23.9375</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>24.146</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>24.363125</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>24.146</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>24.363125</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>20.2075</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>20.433</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>21.033125</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>20.433</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>21.033125</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>20.22</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>20.462</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>21.055625</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>20.462</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>21.055625</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>20.2275</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>20.486</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>21.07625</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>20.486</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>21.07625</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>20.245</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>20.501</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>21.0975</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>20.501</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>21.0975</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>20.2525</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>20.524</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>21.11875</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>20.524</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>21.11875</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>20.235</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>20.545</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>21.135</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>20.545</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>21.135</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>20.2425</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>20.575</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>21.15375</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>20.575</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>21.15375</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>20.2525</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>20.611</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>21.175625</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>20.611</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>21.175625</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>20.26</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>20.654</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>21.196875</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>20.654</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>21.196875</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>20.2675</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>20.703</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>21.21625</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>20.703</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>21.21625</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>34.465</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>38.013125</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>38.013125</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>34.7525</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>36.906</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>38.10875</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>36.906</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>38.10875</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>35.03</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>37.033</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>38.190625</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>37.033</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>38.190625</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>35.3325</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>37.168</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>38.284375</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>37.168</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>38.284375</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>35.64</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>37.301</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>38.364375</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>37.301</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>38.364375</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>35.9</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>37.442</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>38.4325</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>37.442</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>38.4325</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>36.17</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>37.576</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>38.49125</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>37.576</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>38.49125</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>36.4075</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>37.712</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>38.56375</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>37.712</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>38.56375</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>36.65</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>37.856</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>38.6425</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>37.856</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>38.6425</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>36.895</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>37.999</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>38.705625</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>37.999</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>38.705625</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>10.7175</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>10.93</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>11.088125</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>11.088125</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>10.745</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>10.971</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>11.0925</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>10.971</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>11.0925</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>10.7675</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>11.003</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>11.0975</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>11.003</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>11.0975</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>10.7925</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>11.034</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>11.101875</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>11.034</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>11.101875</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>10.795</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>11.072</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>11.10375</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>11.072</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>11.10375</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>10.795</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>11.097</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>11.105</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>11.097</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>11.105</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>10.7975</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>11.116</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>11.105</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>11.116</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>11.105</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>10.795</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>11.132</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>11.1075</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>11.132</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>11.1075</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>10.795</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>11.110625</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>11.110625</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>10.79</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>11.165</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>11.110625</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>11.165</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>11.110625</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
@@ -31971,15 +31651,11 @@
           <t>15.3825</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>16.266</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>16.716875</t>
-        </is>
+      <c r="AN82" t="n">
+        <v>16.266</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>16.716875</v>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
@@ -32358,15 +32034,11 @@
           <t>15.4425</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>16.317</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>16.74875</t>
-        </is>
+      <c r="AN83" t="n">
+        <v>16.317</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>16.74875</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
@@ -32745,15 +32417,11 @@
           <t>15.495</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>16.362</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>16.778125</t>
-        </is>
+      <c r="AN84" t="n">
+        <v>16.362</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>16.778125</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -33132,15 +32800,11 @@
           <t>15.55</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>16.405</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>16.80875</t>
-        </is>
+      <c r="AN85" t="n">
+        <v>16.405</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>16.80875</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -33519,15 +33183,11 @@
           <t>15.6025</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>16.446</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>16.836875</t>
-        </is>
+      <c r="AN86" t="n">
+        <v>16.446</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>16.836875</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
@@ -33906,15 +33566,11 @@
           <t>15.655</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>16.485</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>16.8625</t>
-        </is>
+      <c r="AN87" t="n">
+        <v>16.485</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>16.8625</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -34293,15 +33949,11 @@
           <t>15.7075</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>16.517</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>16.893125</t>
-        </is>
+      <c r="AN88" t="n">
+        <v>16.517</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>16.893125</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -34680,15 +34332,11 @@
           <t>15.765</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>16.555</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>16.9275</t>
-        </is>
+      <c r="AN89" t="n">
+        <v>16.555</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>16.9275</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -35067,15 +34715,11 @@
           <t>15.8375</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>16.606</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>16.963125</t>
-        </is>
+      <c r="AN90" t="n">
+        <v>16.606</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>16.963125</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -35454,15 +35098,11 @@
           <t>15.9125</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>16.659</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>16.99375</t>
-        </is>
+      <c r="AN91" t="n">
+        <v>16.659</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>16.99375</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -35841,15 +35481,11 @@
           <t>19.5825</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>19.699</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>19.98125</t>
-        </is>
+      <c r="AN92" t="n">
+        <v>19.699</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>19.98125</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -36228,15 +35864,11 @@
           <t>19.5375</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>19.693</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>19.985625</t>
-        </is>
+      <c r="AN93" t="n">
+        <v>19.693</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>19.985625</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -36615,15 +36247,11 @@
           <t>19.4775</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>19.679</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>19.994375</t>
-        </is>
+      <c r="AN94" t="n">
+        <v>19.679</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>19.994375</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -37002,15 +36630,11 @@
           <t>19.4325</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>19.663</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>20.00375</t>
-        </is>
+      <c r="AN95" t="n">
+        <v>19.663</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>20.00375</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -37389,15 +37013,11 @@
           <t>19.4025</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>19.664</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+      <c r="AN96" t="n">
+        <v>19.664</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>20.01</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -37776,15 +37396,11 @@
           <t>19.3975</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>19.683</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>20.019375</t>
-        </is>
+      <c r="AN97" t="n">
+        <v>19.683</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>20.019375</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -38163,15 +37779,11 @@
           <t>19.37</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>19.689</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>20.021875</t>
-        </is>
+      <c r="AN98" t="n">
+        <v>19.689</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>20.021875</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -38550,15 +38162,11 @@
           <t>19.3375</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>19.714</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>20.03875</t>
-        </is>
+      <c r="AN99" t="n">
+        <v>19.714</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>20.03875</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -38937,15 +38545,11 @@
           <t>19.3125</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>19.744</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>20.064375</t>
-        </is>
+      <c r="AN100" t="n">
+        <v>19.744</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>20.064375</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -39324,15 +38928,11 @@
           <t>19.2975</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>20.093125</t>
-        </is>
+      <c r="AN101" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>20.093125</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -39711,15 +39311,11 @@
           <t>37.6825</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>39.103</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>38.643125</t>
-        </is>
+      <c r="AN102" t="n">
+        <v>39.103</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>38.643125</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
@@ -40098,15 +39694,11 @@
           <t>37.775</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>39.158</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>38.64749999999999</t>
-        </is>
+      <c r="AN103" t="n">
+        <v>39.158</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>38.64749999999999</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -40485,15 +40077,11 @@
           <t>37.86</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>39.224</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>38.6425</t>
-        </is>
+      <c r="AN104" t="n">
+        <v>39.224</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>38.6425</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
@@ -40872,15 +40460,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>39.269</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>38.636875</t>
-        </is>
+      <c r="AN105" t="n">
+        <v>39.269</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>38.636875</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
@@ -41259,15 +40843,11 @@
           <t>38.15750000000001</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>39.294</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>38.60625</t>
-        </is>
+      <c r="AN106" t="n">
+        <v>39.294</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>38.60625</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
@@ -41646,15 +41226,11 @@
           <t>38.32</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>39.294</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>38.565625</t>
-        </is>
+      <c r="AN107" t="n">
+        <v>39.294</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>38.565625</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
@@ -42033,15 +41609,11 @@
           <t>38.4725</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>39.285</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>38.535</t>
-        </is>
+      <c r="AN108" t="n">
+        <v>39.285</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>38.535</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
@@ -42420,15 +41992,11 @@
           <t>38.68</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>39.291</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>38.51000000000001</t>
-        </is>
+      <c r="AN109" t="n">
+        <v>39.291</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>38.51000000000001</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
@@ -42807,15 +42375,11 @@
           <t>38.91</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>39.295</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>38.48875</t>
-        </is>
+      <c r="AN110" t="n">
+        <v>39.295</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>38.48875</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -43194,15 +42758,11 @@
           <t>39.1825</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>39.307</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>38.45625</t>
-        </is>
+      <c r="AN111" t="n">
+        <v>39.307</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>38.45625</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>

--- a/Result/checksun/橡膠工業.xlsx
+++ b/Result/checksun/橡膠工業.xlsx
@@ -8539,7 +8539,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2114</t>
@@ -10241,7 +10245,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10667,7 +10671,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11093,7 +11097,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11519,7 +11523,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11945,7 +11949,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12371,7 +12375,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12797,7 +12801,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13223,7 +13227,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13649,7 +13653,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14075,7 +14079,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14501,7 +14505,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14927,7 +14931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15353,7 +15357,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15779,7 +15783,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16205,7 +16209,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16631,7 +16635,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17057,7 +17061,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17483,7 +17487,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -17909,7 +17913,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18335,7 +18339,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18759,7 +18763,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2108</t>
@@ -19181,7 +19189,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2108</t>
@@ -19605,7 +19617,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20031,7 +20043,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20457,7 +20469,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -20883,7 +20895,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21309,7 +21321,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21735,7 +21747,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22161,7 +22173,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22587,7 +22599,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23011,7 +23023,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2107</t>
@@ -23433,7 +23449,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2107</t>
@@ -23855,7 +23875,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2107</t>
@@ -29007,7 +29031,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>2105</t>
@@ -29429,7 +29457,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2105</t>
@@ -29851,7 +29883,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2105</t>
@@ -30273,7 +30309,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2105</t>
@@ -30695,7 +30735,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2105</t>
@@ -31119,7 +31163,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31545,7 +31589,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -31971,7 +32015,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32397,7 +32441,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -32823,7 +32867,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33249,7 +33293,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33675,7 +33719,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34101,7 +34145,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -34527,7 +34571,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -34953,7 +34997,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35379,7 +35423,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -35803,7 +35847,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2104</t>
@@ -36225,7 +36273,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2104</t>
@@ -38353,7 +38405,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -38779,7 +38831,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39205,7 +39257,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -39631,7 +39683,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40057,7 +40109,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -40483,7 +40535,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -40907,7 +40959,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2103</t>
@@ -41329,7 +41385,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2103</t>
@@ -47739,7 +47799,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -48165,7 +48225,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48591,7 +48651,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49017,7 +49077,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -49443,7 +49503,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -49869,7 +49929,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -50295,7 +50355,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -50721,7 +50781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -51147,7 +51207,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -51573,7 +51633,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -51999,7 +52059,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
